--- a/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias</t>
+          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,39</t>
+          <t>1,22; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,78</t>
+          <t>1,53; 2,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,54</t>
+          <t>1,54; 2,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,74</t>
+          <t>1,12; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,76</t>
+          <t>1,22; 1,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,4</t>
+          <t>1,46; 2,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,71</t>
+          <t>1,51; 2,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,62</t>
+          <t>1,19; 2,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,96</t>
+          <t>1,3; 1,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,33</t>
+          <t>1,54; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,42</t>
+          <t>1,63; 2,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,01</t>
+          <t>1,25; 1,97</t>
         </is>
       </c>
     </row>
@@ -856,37 +856,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,0</t>
+          <t>1,46; 2,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,21</t>
+          <t>1,48; 2,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,24</t>
+          <t>1,51; 3,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,11</t>
+          <t>1,4; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,08</t>
+          <t>1,56; 2,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,9</t>
+          <t>1,3; 1,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,66</t>
+          <t>1,69; 2,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,22 +896,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,97</t>
+          <t>1,57; 1,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,92</t>
+          <t>1,44; 1,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,63</t>
+          <t>1,73; 2,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,21</t>
+          <t>1,56; 2,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,4</t>
+          <t>1,35; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,35</t>
+          <t>1,76; 3,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,79</t>
+          <t>1,67; 2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,62</t>
+          <t>1,72; 3,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,71</t>
+          <t>1,27; 1,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,22</t>
+          <t>1,52; 2,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,01</t>
+          <t>1,4; 1,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,99</t>
+          <t>1,23; 2,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,91</t>
+          <t>1,36; 1,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,41</t>
+          <t>1,7; 2,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,21</t>
+          <t>1,61; 2,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,71</t>
+          <t>1,57; 2,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,54</t>
+          <t>1,13; 1,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,86</t>
+          <t>1,64; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,19</t>
+          <t>1,4; 2,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,76</t>
+          <t>1,37; 2,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,33</t>
+          <t>1,51; 2,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,92</t>
+          <t>1,37; 1,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,44</t>
+          <t>1,25; 2,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,04</t>
+          <t>1,63; 3,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,91</t>
+          <t>1,41; 1,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,13</t>
+          <t>1,58; 2,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,1</t>
+          <t>1,38; 2,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,64</t>
+          <t>1,66; 2,56</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,79</t>
+          <t>1,41; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,28</t>
+          <t>1,73; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,32</t>
+          <t>1,69; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,19</t>
+          <t>1,56; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,85</t>
+          <t>1,52; 1,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,11</t>
+          <t>1,62; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,95</t>
+          <t>1,67; 1,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,13</t>
+          <t>1,72; 2,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,09</t>
+          <t>1,66; 2,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,53</t>
+          <t>1,24; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,71</t>
+          <t>1,56; 2,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,54</t>
+          <t>1,54; 2,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,72</t>
+          <t>1,13; 1,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,77</t>
+          <t>1,23; 1,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,44; 2,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,86</t>
+          <t>1,53; 2,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,78</t>
+          <t>1,2; 2,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,94</t>
+          <t>1,3; 2,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,29</t>
+          <t>1,57; 2,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,42</t>
+          <t>1,61; 2,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,97</t>
+          <t>1,25; 2,02</t>
         </is>
       </c>
     </row>
@@ -861,37 +861,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,17</t>
+          <t>1,49; 2,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,15</t>
+          <t>1,5; 3,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,14</t>
+          <t>1,43; 2,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,09</t>
+          <t>1,57; 2,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,86</t>
+          <t>1,33; 1,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,63</t>
+          <t>1,66; 2,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,71</t>
+          <t>1,57; 2,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,89</t>
+          <t>1,46; 1,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,82</t>
+          <t>1,71; 2,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,19</t>
+          <t>1,58; 2,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,34</t>
+          <t>1,33; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,63</t>
+          <t>1,8; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,69</t>
+          <t>1,64; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,57</t>
+          <t>1,67; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,75</t>
+          <t>1,27; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,28</t>
+          <t>1,52; 2,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,98</t>
+          <t>1,43; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,03</t>
+          <t>1,22; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,86</t>
+          <t>1,37; 1,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,43</t>
+          <t>1,68; 2,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,17</t>
+          <t>1,6; 2,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,64</t>
+          <t>1,56; 2,61</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,71</t>
+          <t>1,62; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,24</t>
+          <t>1,38; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,84</t>
+          <t>1,38; 2,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,34</t>
+          <t>1,52; 2,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,93</t>
+          <t>1,38; 1,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,42</t>
+          <t>1,24; 2,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,03</t>
+          <t>1,61; 2,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,9</t>
+          <t>1,4; 1,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,16</t>
+          <t>1,56; 2,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,15</t>
+          <t>1,39; 2,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,56</t>
+          <t>1,65; 2,64</t>
         </is>
       </c>
     </row>
@@ -1276,37 +1276,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,78</t>
+          <t>1,42; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,29</t>
+          <t>1,73; 2,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,34</t>
+          <t>1,68; 2,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,2</t>
+          <t>1,61; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,82</t>
+          <t>1,51; 1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,86</t>
+          <t>1,53; 1,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,13</t>
+          <t>1,61; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,75</t>
+          <t>1,51; 1,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,97</t>
+          <t>1,67; 1,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,12</t>
+          <t>1,74; 2,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,07</t>
+          <t>1,67; 2,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,93</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,43</t>
+          <t>1,22; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,82</t>
+          <t>1,44; 2,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,52</t>
+          <t>1,51; 2,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,77</t>
+          <t>1,19; 2,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,8</t>
+          <t>1,24; 2,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,4</t>
+          <t>1,55; 2,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,8</t>
+          <t>1,52; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,68</t>
+          <t>1,12; 1,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,0</t>
+          <t>1,3; 1,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,28</t>
+          <t>1,58; 2,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,38</t>
+          <t>1,66; 2,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,02</t>
+          <t>1,24; 2,0</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,73</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1,63</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,78</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,01</t>
+          <t>1,56; 2,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,17</t>
+          <t>1,34; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,28</t>
+          <t>1,68; 2,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,16</t>
+          <t>1,5; 2,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,08</t>
+          <t>1,43; 2,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,87</t>
+          <t>1,47; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,56</t>
+          <t>1,51; 3,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,72</t>
+          <t>1,35; 2,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,95</t>
+          <t>1,57; 1,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,91</t>
+          <t>1,46; 1,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,7</t>
+          <t>1,7; 2,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,21</t>
+          <t>1,51; 2,12</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,03</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,93</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,36</t>
+          <t>1,26; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,55</t>
+          <t>1,53; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,7</t>
+          <t>1,4; 2,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,4</t>
+          <t>1,2; 1,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,74</t>
+          <t>1,37; 2,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,26</t>
+          <t>1,73; 3,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,05</t>
+          <t>1,67; 2,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,06</t>
+          <t>1,65; 3,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,87</t>
+          <t>1,38; 1,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,43</t>
+          <t>1,7; 2,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,61</t>
+          <t>1,54; 2,75</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,99</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,0</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,55</t>
+          <t>1,51; 2,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,77</t>
+          <t>1,39; 1,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,19</t>
+          <t>1,25; 2,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,83</t>
+          <t>1,6; 3,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,37</t>
+          <t>1,13; 1,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,96</t>
+          <t>1,64; 2,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,66</t>
+          <t>1,39; 2,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,97</t>
+          <t>1,34; 2,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,87</t>
+          <t>1,39; 1,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,17</t>
+          <t>1,57; 2,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,16</t>
+          <t>1,4; 2,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,64</t>
+          <t>1,6; 2,63</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,92</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,8</t>
+          <t>1,52; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,27</t>
+          <t>1,53; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,33</t>
+          <t>1,63; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,2</t>
+          <t>1,59; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,81</t>
+          <t>1,4; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,87</t>
+          <t>1,72; 2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,71; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,21</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,74</t>
+          <t>1,51; 1,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,13</t>
+          <t>1,72; 2,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,09</t>
+          <t>1,63; 2,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
+          <t>Número medio de veces que los menores utilizaron algún servicio de urgencias en los últimos 12 meses (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.438071925285895</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.783429564810774</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.98334312756609</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.673735000011484</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.565251418585965</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.898213923124771</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.925290156314237</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.324950126590017</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.503506664743684</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1.836434252011512</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1.953707008872612</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.489656004827843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 1,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 2,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,71</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 2,69</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 2,39</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 2,78</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,54</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 1,68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 1,96</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 2,33</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 2,42</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 2,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.219863362997069</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.440981503452208</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.509449908945929</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.191407517206486</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.239920537980237</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.550108013850594</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.518399802092187</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.122544860440189</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.299810508126018</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.577188590617897</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.657521008248963</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.244279567216489</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.762619256137508</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.399726150120423</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.713024367489385</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.694827854801717</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.391059345004175</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.777764773612751</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.536614142811114</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.675780519316595</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1.95752977255232</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2.334949460121852</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>2.417880363189011</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2.004150943913324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 2,08</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 1,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 2,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 2,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 2,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 3,24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 2,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,57; 1,97</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 1,92</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,63</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,12</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.778028991975192</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.529305183025993</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.075792005417782</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.927628827899128</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.678124822423031</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.734568960300359</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2.006227444826171</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.635729343331437</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.73640087192248</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.628625198898281</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.039573645860813</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.777525067309128</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.561780371386813</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.340143400488365</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.680999113231974</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.5029328152633</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.430234341062994</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.470228726402423</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.510866896659344</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.35013334308251</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.567697659832344</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.463309235521695</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.700341010048382</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1.51303242240136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,22</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 2,01</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 1,95</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 2,4</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 3,35</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 2,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,65; 3,51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 1,91</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,41</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,21</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.082297074857296</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.898061758182604</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.659690806529497</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.545204558336176</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.998815399081129</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.213548722330395</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3.237228523186772</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.121143269991783</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.970989794681862</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1.915686928077544</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.625121164987742</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>2.124155445507819</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.447303516381961</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.785279727002217</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.673891178780931</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.483696717091638</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.637403032033948</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.31131639851116</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2.02659828311334</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2.338099873293527</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.539607480854626</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.981601952586701</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.840777398368701</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.931539563827979</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,33</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 1,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 2,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 3,02</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 1,54</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,64; 2,86</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 2,19</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 2,71</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 1,91</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,57; 2,13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 2,1</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.262408054719965</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.532198935521395</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.400183306898935</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.201289572689201</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.372230108376652</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.734384009941738</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.671132688023945</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.650812025454593</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.377188327832488</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.697790557772055</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.601412073007816</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.53654598060311</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.713455089912218</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.223802614646693</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.012338909335988</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.953351887187498</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.400336192669527</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.351039773632995</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2.792859595763733</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>3.512542987379921</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.909968709887096</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2.405940912575261</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.210440232852612</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>2.748307237195183</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.842287318693656</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.604104293432245</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.56460505317412</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.140101780756943</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.290053750469476</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.990306633724115</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.697781556869987</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.730975650824844</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.593144907684298</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.788985167664465</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.626667905509085</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>2.00042737147485</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.511457849057053</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.393109636089435</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.252383420992118</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.598530957238799</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.128273230476928</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.64077986693549</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.391210964125997</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.340404995236268</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.390149834962999</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.57198013262984</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.395477817258818</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.60321528613196</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.325220915104465</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.91826888330493</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.441397119839541</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.018722380011726</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.544119916856579</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.860713129598742</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.191497217367975</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.706281660732755</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.909548504665648</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.128618497800554</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.095574598366755</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>2.627497450063758</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,82</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 1,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 1,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,32</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,75</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 1,95</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,13</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.653874766310953</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.667052055658169</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.829099808388757</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.839057176208506</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.559246047567587</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.95066693665458</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.923842161123752</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1.790663312396934</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.610314081910222</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.794890953538632</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.875920111518822</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.815892751960453</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.517190796475913</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.533957283200616</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.625350328521838</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.594982691911127</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.404572583611406</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.715364814633934</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.707208800738527</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1.541333776280006</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.506165429943796</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.670005802589399</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.720522120322726</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.625549578112234</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.822096524924422</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.850526452158602</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.11485078907165</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.170824829565978</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.792786820444103</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.283285123652623</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.322561412158959</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2.175962439952529</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.747753874559038</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1.949470704506522</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.127419887331808</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>2.052742234079716</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
